--- a/public/templates/leads_import_template.xlsx
+++ b/public/templates/leads_import_template.xlsx
@@ -9228,7 +9228,7 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="D4:D503" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Website,Referral,Cold Call,Email,Walk-in,Exhibition,Social Media,Others"</formula1>
+      <formula1>"Website,Referral,Cold Call,Email,Walk-in,Social Media,Digital Marketing,Campaign,Others"</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E503" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low"</formula1>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Website / Referral / Cold Call / Email / Walk-in / Exhibition / Social Media / Others</t>
+          <t>Website / Referral / Cold Call / Email / Walk-in / Social Media / Digital Marketing / Campaign / Others</t>
         </is>
       </c>
     </row>
